--- a/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260701.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260701.xlsx
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>416,000</t>
+          <t>4,334,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>4,334,000</t>
+          <t>416,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>富喬</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>107,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,12 +1437,12 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1481,12 +1481,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,12 +1525,12 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1569,12 +1569,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>富喬</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>107,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
